--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0064.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0064.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Mistune: Exposure</t>
+          <t>Mistune: Phơi Nhiễm</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Twin Nova: Collapsar Blade và Twin Nova: Nebulous Cannon</t>
+          <t>Tân Tinh Song Sinh: Kiếm Hố Đen và Tân Tinh Song Sinh: Pháo Đài Tinh Vân</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Ironhoof</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Mining Reindeer</t>
+          <t>Tuần Lộc Khai Thác</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Flora Reindeer</t>
+          <t>Tuần Lộc Flora</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Spacetrek Explorer</t>
+          <t>Nhà thám hiểm Spacetrek</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Sabercat Prowler</t>
+          <t>Kẻ Rình Rập Mèo Đao</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Vulnerable Core</t>
+          <t>Lõi Dễ Tổn Thương</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Twin Nova: Collapsar Blade và Twin Nova: Nebulous Cannon</t>
+          <t>Tân Tinh Song Sinh: Kiếm Hố Đen và Tân Tinh Song Sinh: Pháo Đài Tinh Vân</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Part Break</t>
+          <t>Phá vỡ bộ phận</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Deflection</t>
+          <t>Né tránh</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Part Break</t>
+          <t>Phá vỡ bộ phận</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Part Break</t>
+          <t>Phá vỡ bộ phận</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Phản đòn các đòn tấn công đặc biệt của Dreamless</t>
+          <t>Né đòn đặc biệt của Dreamless</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Breaking Looming Turmoil</t>
+          <t>Phá Loạn Ảnh Hưởng</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Khiên</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Invisiblity</t>
+          <t>Tàng hình</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Attack Methods</t>
+          <t>Kỹ Thuật Tấn Công</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Expedition Motorbike Controls</t>
+          <t>Điều Khiển Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Boost</t>
+          <t>Tăng cường</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Stars of the Solisylum</t>
+          <t>Những Vì Sao của Solisylum</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Mechascout: Transition</t>
+          <t>Máy trinh sát cơ khí: Transition</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Motorbike Nhảy</t>
+          <t>Nhảy Xe Máy</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Owlwatch Hacking</t>
+          <t>Hack Owlwatch</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Velo Conduit</t>
+          <t>Ống Dẫn Velo</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Grapple Drone</t>
+          <t>Drone Móc</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Tìm kiếm Soliskin</t>
+          <t>Tìm Soliskin</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Soliskin của Solvein Canopy</t>
+          <t>Những giọt Soliskin ở Vòm Solvein</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Băng ghi âm Những Lời Cuối</t>
+          <t>Băng Lời Cuối</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Công cụ: Adaptive Hook</t>
+          <t>Tiện ích: Móc câu thích ứng</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>General Terminal</t>
+          <t>Thiết bị đầu cuối Đại tướng</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Breakable Obstacles</t>
+          <t>Chướng Ngại Vật Có Thể Phá Hủy</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Projector</t>
+          <t>Bộ chiếu</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Projector: Reboot Explorer</t>
+          <t>Máy chiếu: Reboot Explorer</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Projector: Electric Shock</t>
+          <t>Bộ chiếu: Điện Giật</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Projector: Geospider S4</t>
+          <t>Bộ chiếu: Geospider S4</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Projector: Mining Reindeer</t>
+          <t>Máy chiếu: Mining Reindeer</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Motorbike Rail Sliding</t>
+          <t>Trượt Ray Xe Máy</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Rail Sliding</t>
+          <t>Trượt Ray</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Hologram Racetrack</t>
+          <t>Đường Đua Hologram</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Pathfinder Trailer Ramp</t>
+          <t>Dốc Đường Dẫn Đầu Tiên</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>Đang in...</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Voidworm</t>
+          <t>Giun Voidworm</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Những Ngôi Sao của Solisylum</t>
+          <t>Những Vì Sao của Solisylum</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Selecting Transition Direction</t>
+          <t>Đang chọn hướng chuyển tiếp</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Motorbike Nhảy</t>
+          <t>Nhảy Xe Máy</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Activating Owlwatch Hacking</t>
+          <t>Kích hoạt Owlwatch Hacking</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Hacking</t>
+          <t>Đang xâm nhập...</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Velo Conduit</t>
+          <t>Ống Dẫn Velo</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Grapple Drone</t>
+          <t>Drone Móc</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Tìm kiếm Soliskin Bị Mất Tích</t>
+          <t>Tìm kiếm Soliskin thất lạc</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Gathering Soliskin</t>
+          <t>Đang thu thập Soliskin</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Solis Orb</t>
+          <t>Quả Cầu Solis</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Accompanying Soliskin</t>
+          <t>Đồng hành cùng Soliskin</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Băng ghi âm Những Lời Cuối</t>
+          <t>Băng Lời Cuối</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Công cụ: Adaptive Hook</t>
+          <t>Tiện ích: Móc câu thích ứng</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Lahai-Roi Resonance Beacon</t>
+          <t>Đèn Tần Số Lahai-Roi</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>General Terminal</t>
+          <t>Thiết bị đầu cuối Đại tướng</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Breakable Obstacles</t>
+          <t>Chướng Ngại Vật Có Thể Phá Hủy</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Projector</t>
+          <t>Bộ chiếu</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Projector: Zip Zap</t>
+          <t>Máy chiếu: Zip Zap</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Projector: Reboot Explorer</t>
+          <t>Máy chiếu: Reboot Explorer</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Projector: Electric Shock</t>
+          <t>Bộ chiếu: Điện Giật</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Projector: Mining Reindeer</t>
+          <t>Máy chiếu: Mining Reindeer</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Các Loại Trượt Ray</t>
+          <t>Các kiểu Trượt Ray</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Cách Trượt Ray</t>
+          <t>Kỹ thuật Trượt Ray</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Leaping Onto Rail</t>
+          <t>Nhảy Lên Đường Ray</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Switching/Exiting Rail Glide</t>
+          <t>Bật/Tắt Trượt Ray</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Collecting Riding Points</t>
+          <t>Đang thu thập Điểm Cưỡi</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Hologram Racetrack</t>
+          <t>Đường Đua Hologram</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Pathfinder Trailer Ramp</t>
+          <t>Dốc Đường Dẫn Đầu Tiên</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>Đang in...</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Voidworm: Voidmatter Orb</t>
+          <t>Voidworm: Quả Cầu Hư Không</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Voidworm: Energy Pulse</t>
+          <t>Giun Voidworm: Xung Năng Lượng</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Voidworm: Photonic Beam</t>
+          <t>Giun Voidworm: Tia Quang Tử</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Lái qua màn hình xanh để vào Owlwatch Hacking</t>
+          <t>Lái xuyên qua màn hình xanh để vào Owlwatch Hacking</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Đỉnh Uy Danh: Đồ Mới Lạ</t>
+          <t>Đỉnh Vinh Quang: Khởi Đầu Mới</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Đỉnh Uy Danh: Lãnh Địa</t>
+          <t>Peaks of Prestige: Lãnh Địa</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Compilation</t>
+          <t>Khối Smartprint Cube: Biên Dịch</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Bounce Mô-đun</t>
+          <t>Khối Smartprint Cube: Mô-đun Bật Lại</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Faulty Component</t>
+          <t>Khối Smartprint Cube: Linh Kiện Lỗi</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Flow Limiter Mô-đun</t>
+          <t>Khối Smartprint Cube: Mô-đun Hạn Chế Lưu Lượng</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Multiple Blockers</t>
+          <t>Khối Smartprint Cube: Nhiều Vật Chắn</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>About Novelties</t>
+          <t>Về Đồ chơi Mới</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Cách Sử Dụng Đồ Mới Lạ</t>
+          <t>Cách Sử Dụng Vật Phẩm Đặc Biệt</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>About Domains</t>
+          <t>Về các Lĩnh Vực</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Cách Sử Dụng Lãnh Địa</t>
+          <t>Cách Sử Dụng Tổ Tacet</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Cube Blocker</t>
+          <t>Khối Chặn</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Compilation</t>
+          <t>Khối Smartprint Cube: Biên Dịch</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Bounce Mô-đun</t>
+          <t>Mô-đun Nảy</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Faulty Component</t>
+          <t>Linh Kiện Lỗi</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Breaking Faulty Components</t>
+          <t>Phá Hủy Các Bộ Phận Hỏng</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Flow Limiter Mô-đun</t>
+          <t>Mô-đun Hạn Chế Dòng Chảy</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Switching Blockers</t>
+          <t>Đang chuyển đổi vật cản</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Vehicle Looks</t>
+          <t>Ngoại Hình Phương Tiện</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Đẩy cần gạt sang trái hoặc phải để chuyển ray</t>
+          <t>Gạt cần sang trái hoặc phải để đổi đường ray</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Dùng Nhảy trong khi đẩy cần gạt trái/phải để nhảy khỏi ray</t>
+          <t>Nhấn Nhảy đồng thời đẩy cần điều khiển sang trái/phải để bật khỏi đường ray.</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Motorbike Appearance</t>
+          <t>Giao Diện Xe Máy</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Doubled Pawns Matrix: Phi Công</t>
+          <t>Ma trận Tốt Đôi: Phi Công</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Doubled Pawns Matrix: Pilot - Singularity Expansion</t>
+          <t>Ma trận Tốt Đôi: Phi Công - Mở Rộng Điểm Kỳ Dị</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Event Rules</t>
+          <t>Quy Tắc Sự Kiện</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Modes</t>
+          <t>Chế Độ</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Point Rules</t>
+          <t>Quy Tắc Điểm</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Singularity Expansion</t>
+          <t>Mở Rộng Điểm Kỳ Dị</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Kìm Hãm! Hỗn Loạn Di Cư!</t>
+          <t>Thuần Phục! Hỗn Loạn Di Cư!</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Lollo Campaign: Implementation</t>
+          <t>Chiến Dịch Lollo: Thực Thi</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Trôi dạt</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Bounce Nhảy</t>
+          <t>Nhảy Nảy</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Spacetrek Convoy Vật tư</t>
+          <t>Vật tư Đoàn vận tải Spacetrek</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Route Network Blockage</t>
+          <t>Tắc Nghẽn Mạng Lưới Tuyến Đường</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Spacetrek Convoy Vật tư</t>
+          <t>Vật tư Đoàn vận tải Spacetrek</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Route Network Blockage</t>
+          <t>Tắc Nghẽn Mạng Lưới Tuyến Đường</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Smartprint Cube</t>
+          <t>Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Smartprint Cube</t>
+          <t>Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Đua Startorch</t>
+          <t>Đua Xe Sao Chổi</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Mở khóa xe máy thám hiểm trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên Băng Giá"</t>
+          <t>Mở khóa xe máy thám hiểm trong Nhiệm Vụ Chính "What Burns Beneath Frostlands"</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Rời khỏi Startorch Academy sau khi đến nơi</t>
+          <t>Rời khỏi Học viện Startorch sau khi đến nơi</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Deck Composition</t>
+          <t>Thành phần Bộ bài</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Deck Build</t>
+          <t>Xây dựng Bộ bài</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Echo Category</t>
+          <t>Loại Echo</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>New Cards</t>
+          <t>Thẻ Mới</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Lộ Trình Sao Đan Xen</t>
+          <t>Những Con Đường Sao Đan Xen</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Veins of the Frostlands</t>
+          <t>Mạch Đất Vùng Băng Giá</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Nhặt Voidmatter Orbs để nạp lại Energy Pulse</t>
+          <t>Thu thập Quả Cầu Hư Không để nạp lại Xung Năng Lượng</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Nhặt Voidmatter Orbs để nạp lại Energy Pulse</t>
+          <t>Thu thập Quả Cầu Hư Không để nạp lại Xung Năng Lượng</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Perpetual Spark</t>
+          <t>Tia Lửa Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Hãm Lại! Migration Mayhem!—Chi Tiết Chế Độ Dễ và Khó</t>
+          <t>Thuần Phục! Hỗn Loạn Di Cư!—Chi Tiết Chế Độ Dễ Và Khó</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Quà Tặng của Solsworn</t>
+          <t>Quà Tặng Của Solsworn</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Event Quests</t>
+          <t>Nhiệm Vụ Sự Kiện</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Data Modification</t>
+          <t>Điều Chỉnh Dữ Liệu</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Lối chơi Info</t>
+          <t>Thông Tin Trò Chơi</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Trùm</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Tinh Anh</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Zap Mô-đun và Tăng Cường</t>
+          <t>Mô-đun Tia Sét và Tăng Cường</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Repeater Mô-đun</t>
+          <t>Mô-đun Bộ lặp</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Shotgun Mô-đun</t>
+          <t>Mô-đun Súng Ngắn</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Orbital Strike Protocol</t>
+          <t>Giao Thức Đòn Đánh Quỹ Đạo</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Sustained Combustion Protocol</t>
+          <t>Giao Thức Đốt Cháy Liên Tục</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Guided Missile Protocol</t>
+          <t>Giao Thức Tên Lửa Điều Khiển</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Endless Track</t>
+          <t>Bản nhạc Vô Tận</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Di Chuyển</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Track Buff</t>
+          <t>Bản nhạc Buff</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Enemy Encounter</t>
+          <t>Chạm trán kẻ địch</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Boss Fight</t>
+          <t>Đối Đầu Trùm</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Thất Bại và Lưu Lại Thử Thách</t>
+          <t>Thử Thách Thất Bại và Lưu Lại</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Elite Enemy</t>
+          <t>Kẻ địch Cấp Tinh Anh</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Zap Mô-đun</t>
+          <t>Mô-đun Tia Sét</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Repeater Mô-đun</t>
+          <t>Mô-đun Bộ lặp</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Shotgun Mô-đun</t>
+          <t>Mô-đun Súng Ngắn</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Orbital Strike Protocol</t>
+          <t>Giao Thức Đòn Đánh Quỹ Đạo</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Sustained Combustion Protocol</t>
+          <t>Giao Thức Đốt Cháy Liên Tục</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Guided Missile Protocol</t>
+          <t>Giao Thức Tên Lửa Điều Khiển</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Endless Track</t>
+          <t>Bản nhạc Vô Tận</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Bầu Không Khí Vui Vẻ</t>
+          <t>Tần Số Hân Hoan</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Card Game: Overview</t>
+          <t>Trò chơi Thẻ: Tổng Quan</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Card Game: Basic Rules</t>
+          <t>Trò chơi Thẻ: Luật Cơ Bản</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Trang trí tiệc</t>
+          <t>Trang trí nhóm</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Vibe Gauge</t>
+          <t>Thang Đo Cảm Xúc</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Trang trí tiệc</t>
+          <t>Trang trí nhóm</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Trò Chơi Thẻ</t>
+          <t>Trò chơi Thẻ</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Basics</t>
+          <t>Cơ bản</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Pair</t>
+          <t>Cặp đôi</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Crownless Card</t>
+          <t>Thẻ Crownless</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Rover's Skill</t>
+          <t>Kỹ Năng Của Rover</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Decor Design</t>
+          <t>Thiết Kế Trang Trí</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Saving Decor Deign</t>
+          <t>Lưu Trang Trí Thiết Kế</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Obtaining Decor</t>
+          <t>Đang thu thập Trang trí</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Bước chân</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Digital Shadow Modules</t>
+          <t>Khối Smartprint Cube: Các Mô-đun Bóng Ma Kỹ Thuật Số</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Laser Beam Mô-đun</t>
+          <t>Khối Smartprint Cube: Mô-đun Tia Laser</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Digital Shadow Mô-đun</t>
+          <t>Khối Smartprint Cube: Mô-đun Bóng Ma Kỹ Thuật Số</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Digital Shadow Mô-đun</t>
+          <t>Khối Smartprint Cube: Mô-đun Bóng Ma Kỹ Thuật Số</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Laser Beam Mô-đun</t>
+          <t>Khối Smartprint Cube: Mô-đun Tia Laser</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Smartprint Cube: Blocker Fusing</t>
+          <t>Khối Smartprint Cube: Hợp Nhất Vật Chắn</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>New Expansion Mô-đun</t>
+          <t>Mô-đun Mở Rộng Mới</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Expedition Motorbike: Glacier Track</t>
+          <t>Xe Máy Thám Hiểm: Đường Vượt Băng Giá</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>New Expansion Mô-đun</t>
+          <t>Mô-đun Mở Rộng Mới</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Switch Expansion Mô-đun</t>
+          <t>Chuyển mô-đun mở rộng</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Instant Veto</t>
+          <t>Phủ quyết tức thì</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Time Reverse</t>
+          <t>Thời gian đảo ngược</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Sharp Instinct</t>
+          <t>Bản năng sắc bén</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Mind Scalpel</t>
+          <t>Dao Phẫu Tâm Thức</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Thẻ Ngẫu nhiên</t>
+          <t>Quân Bài Bất Ngờ</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Aemeath -  Journey With Bạn</t>
+          <t>Aemeath - Hành Trình Cùng Người</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Nhà Thám Hiểm Vô Danh - Reckoning of Stars</t>
+          <t>Nhà Thám Hiểm Vô Danh - Sự Thanh Toán Của Những Vì Sao</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Nameless Explorer - Tune Strain Mark</t>
+          <t>Nhà Thám Hiểm Vô Danh - Dấu Ấn Giai Điệu Tacet</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Kronaclaws và Kronablights</t>
+          <t>Móng Vuốt Hắc Ám và Kẻ Ám Sương</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Projector: Icebreaker</t>
+          <t>Máy chiếu: Icebreaker</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Projector: Cave Slide</t>
+          <t>Bộ chiếu: Trượt Hang</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Voidmatter Forcefield</t>
+          <t>Lớp chắn lực Vật Chất Hư Không</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Glacier Probe</t>
+          <t>Thám Tử Băng Hà</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Thử Thách Xe Máy: Icespike Track</t>
+          <t>Thử Thách Xe Máy: Đường Đua Gai Băng</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Expedition Motorbike Hỗ Trợ Modules</t>
+          <t>Mô-đun Hỗ Trợ Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Mô-đun Adapter</t>
+          <t>Bộ chuyển đổi Mô-đun</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Void Barrier</t>
+          <t>Rào Cản Hư Không</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Condensed Exoenergy</t>
+          <t>Năng Lượng Ngoại Sinh Kết Tinh</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Thiết Bị Truyền Tải Khối Etheric Sea Droplets</t>
+          <t>Thiết Bị Truyền Dẫn Khối Lượng Giọt Biển Nguyên Tố</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Exoenergy</t>
+          <t>Năng Lượng Exo</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Soliskin Guide</t>
+          <t>Hướng Dẫn Thu Thập Soliskin</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Frostlands Surface: Void Storm</t>
+          <t>Bề Mặt Vùng Đất Băng: Bão Hư Không</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Thẻ Ngẫu nhiên</t>
+          <t>Quân Bài Bất Ngờ</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Exoswarm Containment Unit</t>
+          <t>Đơn vị Kiềm Chế Exoswarm</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Off Course</t>
+          <t>Lệch hướng</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Journey With Bạn</t>
+          <t>Hành Trình Bên Em</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Form Switch</t>
+          <t>Chuyển Hình Thái</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Synchronization Rate</t>
+          <t>Tỷ Lệ Đồng Bộ</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Resonance Rate</t>
+          <t>Tỷ Lệ Cộng Hưởng</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Reckoning of Stars</t>
+          <t>Thanh Toán Của Những Vì Sao</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Tune Strain Mark</t>
+          <t>Dấu hiệu Tune Strain</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Kronaclaws và Kronablights</t>
+          <t>Móng Vuốt Hắc Ám và Kẻ Ám Sương</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Frost Armor State</t>
+          <t>Trạng thái Giáp Băng</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Cho Ngà</t>
+          <t>Tấn công Ngà Tacet</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Projector: Icebreaker</t>
+          <t>Máy chiếu: Icebreaker</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Projector: Cave Slide</t>
+          <t>Bộ chiếu: Trượt Hang</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Using Voidmatter Forcefield</t>
+          <t>Kích hoạt Lực Trường Hư Không</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Glacier Probe</t>
+          <t>Thám Tử Băng Hà</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Thử Thách Xe Máy: Icespike Track</t>
+          <t>Thử Thách Xe Máy: Đường Đua Gai Băng</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Expedition Motorbike Hỗ Trợ Modules</t>
+          <t>Mô-đun Hỗ Trợ Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Mô-đun Adapter</t>
+          <t>Bộ chuyển đổi Mô-đun</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Unstable Frequency Core</t>
+          <t>Lõi Tần Số Bất Ổn</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Stable Adaptive Mô-đun</t>
+          <t>Mô-đun Thích Ứng Ổn Định</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Unstable Barrier</t>
+          <t>Lớp Chắn Bất Ổn</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Void Barrier</t>
+          <t>Rào Cản Hư Không</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Condensed Exoenergy</t>
+          <t>Năng Lượng Ngoại Sinh Kết Tinh</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Stabilizing Droplets</t>
+          <t>Giọt Ổn Định</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Platform Relay</t>
+          <t>Trạm Trung Chuyển</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Exoenergy</t>
+          <t>Năng Lượng Exo</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Contaminated Giant Soliskin</t>
+          <t>Da Solis Khổng Lồ Bị Nhiễm Khuẩn</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Xây Dựng Tuyến Đường</t>
+          <t>Đang Xây Dựng Tuyến Đường</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Di Chuyển Soliskin</t>
+          <t>Di Chuyển Da Mặt Trời</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Frostlands Surface: Void Storm</t>
+          <t>Bề Mặt Vùng Đất Băng: Bão Hư Không</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Ice Wall</t>
+          <t>Tường Băng</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Boost</t>
+          <t>Tăng cường</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Switching Driving POV</t>
+          <t>Đang chuyển đổi góc nhìn lái</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Login Days</t>
+          <t>Số Ngày Đăng Nhập</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Phần Thưởng</t>
+          <t>Phần thưởng</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Exam Lineup</t>
+          <t>Danh Sách Thi</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Buff Cấp Độ GPA</t>
+          <t>HIỆU ỨNG CẤP ĐỘ GPA</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Exam Details</t>
+          <t>Chi tiết bài kiểm tra</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Hiệp sĩ Hoang dã</t>
+          <t>Hiệp Sĩ Hoang Dã</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Tăng Cấp Độ GPA</t>
+          <t>Đang tăng Cấp Độ GPA</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Loại bỏ Echo thông minh</t>
+          <t>Loại Bỏ Hồi Âm Thông Minh</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Bay theo nhịp điệu</t>
+          <t>Bay theo Nhịp Điệu</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Points Collection Mode</t>
+          <t>Chế Độ Thu Thập Điểm</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Tier-1 Glitched Block</t>
+          <t>Khối Nhiễu Cấp 1</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Damaged Data Block</t>
+          <t>Khối Dữ Liệu Hư Hỏng</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Medal Collection Mode</t>
+          <t>Chế độ Sưu Tập Huy Chương</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Lahai-Roi Blocks: Infinite</t>
+          <t>Lahai-Roi Blocks: Vô tận</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Tier-2 Glitched Block</t>
+          <t>Khối Nhiễu Cấp 2</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Mở khóa xe máy thám hiểm trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên Băng Giá"</t>
+          <t>Mở khóa xe máy thám hiểm trong Nhiệm Vụ Chính "What Burns Beneath Frostlands"</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Vào Chương trình Ký ức!</t>
+          <t>Tiến vào Chương Trình Ký Ức!</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Tàu vũ trụ tự động điều khiển khi gặp Nốt Nhạc Quay</t>
+          <t>Phi thuyền sẽ tự động cơ động khi gặp Nốt Chuyển Hướng.</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Tàu vũ trụ tự động điều khiển khi gặp Nốt Nhạc Quay</t>
+          <t>Phi thuyền sẽ tự động cơ động khi gặp Nốt Chuyển Hướng.</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Tàu vũ trụ tự động điều khiển khi gặp Nốt Nhạc Quay</t>
+          <t>Phi thuyền sẽ tự động cơ động khi gặp Nốt Chuyển Hướng.</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Giữ Nút Vàng để đánh Nốt Vàng Dài</t>
+          <t>Giữ Nút Vàng để đánh các Nốt Nhạc Vàng Dài</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Giữ Nút Vàng để đánh Nốt Vàng Dài</t>
+          <t>Giữ Nút Vàng để đánh các Nốt Nhạc Vàng Dài</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Giữ Nút Vàng để đánh Nốt Vàng Dài</t>
+          <t>Giữ Nút Vàng để đánh các Nốt Nhạc Vàng Dài</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Stellar Orbit Beats Basics</t>
+          <t>Cơ bản về Nhịp Quỹ Đạo Tinh Tú</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Stellar Orbit Beats Basics</t>
+          <t>Cơ bản về Nhịp Quỹ Đạo Tinh Tú</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Giai Đoạn 2 Quỹ Đạo Sao</t>
+          <t>Nhịp Quỹ Đạo Tinh Tú Giai đoạn 2</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Music Notes</t>
+          <t>Nốt nhạc</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Directional Notes</t>
+          <t>Nốt Nhạc Định Hướng</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Yellow Notes</t>
+          <t>Nốt Nhạc Vàng</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Music Notes</t>
+          <t>Nốt nhạc</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Directional Notes</t>
+          <t>Nốt Nhạc Định Hướng</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Yellow Notes</t>
+          <t>Nốt Nhạc Vàng</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Flying Speed</t>
+          <t>Tốc Độ Bay</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Full Speed Mode</t>
+          <t>Chế Độ Tốc Độ Tối Đa</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Triangle Mode</t>
+          <t>Chế Độ Tam Giác</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Freefly Mode</t>
+          <t>Chế Độ Bay Tự Do</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Basics</t>
+          <t>Cơ bản</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Sẵn sàng Né Tránh!</t>
+          <t>Chuẩn bị né đòn!</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Resonance Skill</t>
+          <t>Kỹ năng Resonator</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Resonance Skill</t>
+          <t>Kỹ năng Resonator</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Resonance Skill</t>
+          <t>Kỹ năng Resonator</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Resonance Skill</t>
+          <t>Kỹ năng Resonator</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Resonance Skill</t>
+          <t>Kỹ năng Resonator</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Resonance Skill</t>
+          <t>Kỹ năng Resonator</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Sử dụng Rune: Switch để thay đổi trạng thái của Switchgate</t>
+          <t>Dùng Rune: Switch để thay đổi trạng thái của Switchgate.</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Sử dụng Rune: Switch để thay đổi trạng thái của Switchgate</t>
+          <t>Dùng Rune: Switch để thay đổi trạng thái của Switchgate.</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Endstate Matrix: Singularity Expansion</t>
+          <t>Ma Trận Tận Thế: Mở Rộng Điểm Kỳ Dị</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Thử Thách Khu Vực</t>
+          <t>Khu Vực Thử Thách</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Earning Points</t>
+          <t>Tích Điểm</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Singularity Expansion</t>
+          <t>Mở Rộng Điểm Kỳ Dị</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Viral Contamination</t>
+          <t>Ô Nhiễm Virus</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Thi Hiệp Sĩ Hoang Dã</t>
+          <t>Hiệp Sĩ Hoang Dã: Sách Hướng Dẫn Thi</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Điểm Chính Hiệp Sĩ Hoang Dã</t>
+          <t>Hiệp Sĩ Hoang Dã: Điểm Chính</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Points Collection Mode</t>
+          <t>Chế Độ Thu Thập Điểm</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Tier-1 Glitched Block</t>
+          <t>Khối Nhiễu Cấp 1</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Medal Collection Mode</t>
+          <t>Chế độ Sưu Tập Huy Chương</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Damaged Data Block</t>
+          <t>Khối Dữ Liệu Hư Hỏng</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Tier-2 Glitched Block</t>
+          <t>Khối Nhiễu Cấp 2</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Exam Scope</t>
+          <t>Phạm Vi Thi</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Nâng Cấp Độ GPA</t>
+          <t>Đang tăng Cấp GPA</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Saving Progress</t>
+          <t>Đang lưu tiến trình</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Cách Làm Yếu Người Giám Khảo</t>
+          <t>Cách Làm Suy Yếu Giám Khảo</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Points Collection Mode I</t>
+          <t>Chế Độ Thu Thập Điểm I</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Points Collection Mode II</t>
+          <t>Chế Độ Thu Thập Điểm II</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Tier-1 Glitched Block</t>
+          <t>Khối Nhiễu Cấp 1</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Medal Collection Mode</t>
+          <t>Chế độ Sưu Tập Huy Chương</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Damaged Data Block</t>
+          <t>Khối Dữ Liệu Hư Hỏng</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Tier-2 Glitched Block</t>
+          <t>Khối Nhiễu Cấp 2</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Switchgate</t>
+          <t>Cổng Chuyển Đổi</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Electronic Keyboard</t>
+          <t>Đàn Phím Điện Tử</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Rune: Switch</t>
+          <t>Bùa: Công Tắc</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Rune: Khóa và Chìa Khóa</t>
+          <t>Bùa: Ổ Khóa và Chìa Khóa</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Disruption Rune</t>
+          <t>Rune Phá Vỡ</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Drum Set</t>
+          <t>Bộ trống</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Lahai-Roi Blocks: Infinite</t>
+          <t>Lahai-Roi Blocks: Vô tận</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Switchgate</t>
+          <t>Cổng Chuyển Đổi</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Electronic Keyboard</t>
+          <t>Đàn Phím Điện Tử</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Rune: Switch</t>
+          <t>Bùa: Công Tắc</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Rune: Key</t>
+          <t>Bùa: Chìa Khóa</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Rune: Lock</t>
+          <t>Bùa: Ổ Khóa</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Disruption Rune</t>
+          <t>Rune Phá Vỡ</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Drumhead</t>
+          <t>Mặt trống</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Hi-hat</t>
+          <t>Tách tách</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Microphonephone</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Người nói</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Lahai-Roi Blocks: Infinite I</t>
+          <t>Lahai-Roi Blocks: Vô tận I</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Lahai-Roi Blocks: Infinite II</t>
+          <t>Lahai-Roi Blocks: Vô tận II</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Quà tặng Đại Lễ</t>
+          <t>Mộng Đại Lễ</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Vượt Sóng: Lãnh Nguyên Roya</t>
+          <t>Vượt Qua Những Con Sóng: Roya Frostlands</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Bountiful Waves</t>
+          <t>Sóng Dạt Dào</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Dimmr Traces</t>
+          <t>Dấu Vết Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Hiệp Sĩ Hoang Dã - Ném Bóng</t>
+          <t>Hiệp Sĩ Hoang Dã - Ném Đá</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Hiệp Sĩ Hoang Dã - Ném Bóng</t>
+          <t>Hiệp Sĩ Hoang Dã - Ném Đá</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 1</t>
+          <t>Đồng Bộ Thế Giới: Phần 1</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 2</t>
+          <t>Đồng Bộ Thế Giới: Phần 2</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Trang phục Accessory</t>
+          <t>Phụ Kiện Trang Phục</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Vực Sâu Ảo Cảnh: Giấc Mộng Sắc Màu</t>
+          <t>Tổ Tacet Ảo Ảnh: Giấc Mộng Sắc Màu</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Voidmatter Blocks</t>
+          <t>Khối Vật Chất Hư Không</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Hỗ trợ Khảo Sát Đồng Bằng Dimmr</t>
+          <t>Hỗ trợ Khảo sát Đồng bằng Dimmr</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Restoration Project</t>
+          <t>Dự Án Phục Hồi</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Advancing Survey Objectives</t>
+          <t>Tiến hành khảo sát mục tiêu</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Basic Controls</t>
+          <t>Điều Khiển Cơ Bản</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Vật Phá Hủy &amp; Rơi Vật Phẩm</t>
+          <t>Vật thể phá hủy &amp; Vật phẩm rơi</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Burst</t>
+          <t>Kích Hoạt</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Prism Formation Mechanics</t>
+          <t>Cơ Chế Hình Thành Lăng Kính</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Chuyến Tham quan Tìm Kiếm Dải Ngân Hà</t>
+          <t>Chuyến Du Ngoạn Kiếm Thức Thiên Hà</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>New Mechanism</t>
+          <t>Cơ Chế Mới</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Boss Mechanics</t>
+          <t>Cơ Chế Đầu Sỏ</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>New Mechanism</t>
+          <t>Cơ Chế Mới</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Boss Mechanics</t>
+          <t>Cơ Chế Đầu Sỏ</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>New Mechanism</t>
+          <t>Cơ Chế Mới</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Boss Mechanics</t>
+          <t>Cơ Chế Đầu Sỏ</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>New Mechanism</t>
+          <t>Cơ Chế Mới</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Boss Mechanics</t>
+          <t>Cơ Chế Đầu Sỏ</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Boss Mechanics</t>
+          <t>Cơ Chế Đầu Sỏ</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Boss Mechanics</t>
+          <t>Cơ Chế Đầu Sỏ</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Boss Mechanics</t>
+          <t>Cơ Chế Đầu Sỏ</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Exclusive ROM</t>
+          <t>ROM Độc Quyền</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Dọn Dẹp Dị Thường Xung Quanh Cây Già Voidbane</t>
+          <t>Dọn dẹp Dị Thường quanh Voidbane Eldertrees</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Khôi Phục Sự Sinh Trưởng Của Cây Già Voidbane</t>
+          <t>Khôi Phục Sự Phát Triển Của Cây Già Hư Không</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Collecting Restoratives</t>
+          <t>Đang thu thập Vật phẩm Hồi phục</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Restoration Completion</t>
+          <t>Tiến Độ Phục Hồi</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Collecting "Prism Fruit"</t>
+          <t>Đang thu thập "Quả Lăng Kính"</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Completing Survey Objectives</t>
+          <t>Hoàn Thành Mục Tiêu Khảo Sát</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Flippers/Launch</t>
+          <t>Ván Trượt/Nhảy Xa</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Xông Pha</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Pinball Finisher Skill</t>
+          <t>Kỹ Năng Kết Liễu Pinball</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Vật Phá Hủy &amp; Rơi Vật Phẩm</t>
+          <t>Vật thể phá hủy &amp; Vật phẩm rơi</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Burst &amp; Đồng Hồ Burst</t>
+          <t>Kích Hoạt &amp; Thanh Kích Hoạt</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Prism Formation Mechanics</t>
+          <t>Cơ Chế Hình Thành Lăng Kính</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Galaxy Abundance Collection</t>
+          <t>Bộ Sưu Tập Sung Túc Vô Tận</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>One-Way Gate</t>
+          <t>Cổng Một Chiều</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Obstacles</t>
+          <t>Chướng Ngại</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Omni-Bounce</t>
+          <t>Phản Xạ Toàn Phần</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Directional Bounce</t>
+          <t>Nảy Theo Hướng</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Sư Tử Nữ Vinh Quang</t>
+          <t>Sư Tử Vinh Quang - Giai Đoạn Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Black Hole</t>
+          <t>Hố Đen</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Khúc Bi Ca Của Kẻ Tàn Phai</t>
+          <t>Khúc Bi Ca Sa Ngã</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Nameless Explorer</t>
+          <t>Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Pinball Exclusive ROMs</t>
+          <t>ROM Độc Quyền Pinball</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Expedition Motorbike: Aerial Tactics</t>
+          <t>Xe Máy Thám Hiểm: Chiến Thuật Trên Không</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Chiến thuật trên không xe máy</t>
+          <t>Chiến thuật xe máy trên không</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Aerial Dash</t>
+          <t>Đột Kích Trên Không</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Charged Leap</t>
+          <t>Nhảy Tấn Công đã nạp</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Thử Thách Light Builder</t>
+          <t>Thử Thách Thợ Xây Ánh Sáng</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Voidcreeps</t>
+          <t>Sinh Vật Hư Không</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Lumescribe Component</t>
+          <t>Bộ phận Ghi Âm Lumen</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Lumescribe Component: Hoverdroid</t>
+          <t>Bộ phận Ghi Âm Lumen: Hoverdroid</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Stalaglow Cavern</t>
+          <t>Hang Stalaglow</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Royan Rune Fragment</t>
+          <t>Mảnh Rune Royan</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Nivora Doll</t>
+          <t>Búp Bê Nivora</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Solight Dial</t>
+          <t>Đồng Hồ Solight</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Soliskin Platform</t>
+          <t>Bệ Đỡ Soliskin</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Freezing</t>
+          <t>Đang đóng băng</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Solvein Heartwood Branch</t>
+          <t>Nhánh Lòng Gỗ Solvein</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>"Cấp Độ Bí Mật" của Denia</t>
+          <t>"Cấp độ bí mật" của Denia</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Voidmatter Blocks</t>
+          <t>Khối Vật Chất Hư Không</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Voidmatter Blocks: Infinite</t>
+          <t>Khối Vật Chất Hư Không: Vô Hạn</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Lumescribe Emitter</t>
+          <t>Bộ Phát Sáng Lumen</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Thử Thách Đường Đua Xe Máy: Vòng Điểm</t>
+          <t>Thử Thách Đường Đua Xe Máy: Vòng Tính Điểm</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Thử Thách Đường Đua Xe Máy: Đường Đua Kỹ Xảo</t>
+          <t>Thử Thách Đường Đua Xe Máy: Stunt Track</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Snowtrace</t>
+          <t>Dấu Vết Tuyết</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Soliskin Puff</t>
+          <t>Bánh Bông Soliskin</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Residual Voidmatter</t>
+          <t>Vật chất Hư Không còn sót lại</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Void Storm Zone</t>
+          <t>Khu Vực Bão Hư Không</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Light Builder</t>
+          <t>Thợ Xây Ánh Sáng</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Voidcreeps</t>
+          <t>Sinh Vật Hư Không</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Lumescribe Component I</t>
+          <t>Bộ phận Ghi Âm Lumen I</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Lumescribe Component II</t>
+          <t>Bộ phận Ghi Âm Lumen II</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Lumescribe Component III</t>
+          <t>Bộ phận Ghi Âm Lumen III</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Lumescribe Component: Hoverdroid</t>
+          <t>Bộ phận Ghi Âm Lumen: Hoverdroid</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Stalaglow Cavern</t>
+          <t>Hang Stalaglow</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Sensing Runes</t>
+          <t>Dấu Hiệu Cảm Nhận</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Aligning Runes</t>
+          <t>Đang xếp rune</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Nivora Doll</t>
+          <t>Búp Bê Nivora</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Solight Dial</t>
+          <t>Đồng Hồ Solight</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Tilting</t>
+          <t>Nghiêng Ngả</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Blocking Light</t>
+          <t>Ánh sáng chặn</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Freezing</t>
+          <t>Đang đóng băng</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Solvein Heartwood Branch</t>
+          <t>Nhánh Lòng Gỗ Solvein</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>"Cấp Độ Bí Mật" của Denia</t>
+          <t>"Cấp độ bí mật" của Denia</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Voidmatter Blocks I</t>
+          <t>Khối Vật Chất Hư Không I</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Voidmatter Blocks II</t>
+          <t>Khối Vật Chất Hư Không II</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Voidmatter Blocks III</t>
+          <t>Khối Vật Chất Hư Không III</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Voidmatter Blocks: Infinite I</t>
+          <t>Khối Vật Chất Hư Không: Vô Hạn I</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Voidmatter Blocks: Infinite II</t>
+          <t>Khối Vật Chất Hư Không: Vô Hạn II</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Voidmatter Blocks: Infinite III</t>
+          <t>Khối Vật Chất Hư Không: Vô Hạn III</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Activating Lumescribe Emitters</t>
+          <t>Đang kích hoạt bộ phát Lumescribe</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Rock Mirrors</t>
+          <t>Những Tấm Gương Đá</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Origami Construct: White Bird</t>
+          <t>Cỗ Máy Origami: Chim Trắng</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Thử Thách Đường Đua Xe Máy: Vòng Điểm</t>
+          <t>Thử Thách Đường Đua Xe Máy: Vòng Tính Điểm</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Thử Thách Đường Đua Xe Máy: Đường Đua Kỹ Xảo</t>
+          <t>Thử Thách Đường Đua Xe Máy: Stunt Track</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Snowtrace</t>
+          <t>Dấu Vết Tuyết</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Soliskin Puff</t>
+          <t>Bánh Bông Soliskin</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Residual Voidmatter</t>
+          <t>Vật chất Hư Không còn sót lại</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Dimmr Plains - Void Storm Zone</t>
+          <t>Đồng Bằng Dimmr - Vùng Bão Hư Không</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Cubie Derby: Championship</t>
+          <t>Đua Cubie: Giải Vô Địch</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Cubie Derby: Quy Tắc &amp; Hỗ Trợ</t>
+          <t>Giải Đua Cubie: Luật &amp; Hỗ Trợ</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Cubie Derby: Quy Tắc &amp; Hỗ Trợ</t>
+          <t>Giải Đua Cubie: Luật &amp; Hỗ Trợ</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Depths of Illusive Realm: Sắc Màu Ảo Ảnh</t>
+          <t>Tổ Tacet Ảo Ảnh: Giấc Mộng Sắc Màu</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Depths of Illusive Realm: Điều Chỉnh Tương Tác</t>
+          <t>Tổ Tacet Ảo Ảnh: Điều Chỉnh Meme</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Race Hướng dẫn</t>
+          <t>Hướng dẫn đua</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Race Schedules</t>
+          <t>Lịch trình đua</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Quy Tắc Đua I: Di Chuyển &amp; Xếp Chồng</t>
+          <t>Luật đua I: Di chuyển &amp; Xếp chồng</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Quy Tắc Đua II: Kỹ Năng &amp; Cơ Chế</t>
+          <t>Luật đua II: Kỹ năng &amp; Cơ chế</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Hoàn Thành &amp; Thăng Tiến</t>
+          <t>Hoàn Thành &amp; Tiến Bộ</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Advancement Rules</t>
+          <t>Quy tắc thăng tiến</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Turn Flow</t>
+          <t>Dòng Chảy Xoay Chuyển</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Cube Stacking</t>
+          <t>Xếp Chồng Khối</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Cube Hỗ Trợ</t>
+          <t>Khối Lập Phương Ủng Hộ</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Race Overview</t>
+          <t>Tổng quan cuộc đua</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Advancement Rules</t>
+          <t>Quy tắc thăng tiến</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Xem Lại Trận Đấu &amp; Tóm Tắt Cuộc Đua</t>
+          <t>Xem lại cuộc đua và tóm tắt</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Depths of Illusive Realm: Sắc Màu Ảo Ảnh</t>
+          <t>Tổ Tacet Ảo Ảnh: Giấc Mộng Sắc Màu</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Depths of Illusive Realm: Thám Hiểm</t>
+          <t>Tổ Tacet Ảo Ảnh: Thám Hiểm</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Depths of Illusive Realm: Điều Chỉnh Tương Tác</t>
+          <t>Tổ Tacet Ảo Ảnh: Điều Chỉnh Meme</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Origami Construct</t>
+          <t>Cỗ Máy Origami</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Origami Construct</t>
+          <t>Cỗ Máy Origami</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Dimmr Travelogue</t>
+          <t>Nhật Ký Hành Trình Dimmr</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Resonance Skill DMG+</t>
+          <t>Sát Thương Resonance Skill+</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Tăng Spectro DMG</t>
+          <t>Sát Thương Spectro+</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Havoc DMG+</t>
+          <t>Sát Thương Havoc +10%.</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Havoc DMG+</t>
+          <t>Sát Thương Havoc+</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
